--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -1687,7 +1687,7 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>No asset packs or Starter Content per design doc.</t>
+          <t>No asset packs or Starter Content per design doc. Outdoor surface approach and enterable entrance building blocked out 2026-07-27 using the engine modeling tools; interior vault rooms outstanding.</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="10" min="1" max="1"/>
@@ -2596,6 +2596,38 @@
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="12" t="n"/>
     </row>
+    <row r="31" ht="56.1" customHeight="1" s="10">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Level Geometry Collision</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Walk the blockout level end to end in PIE. Confirm the player is blocked by every wall, floor, and the exterior of the entrance building. Confirm the player can pass through each carved doorway and is still blocked by the surrounding wall.</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>(1) Player clipped through all geometry created with the engine modeling tools. (2) After collision was added, the carved doorways became impassable.</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log for either issue.</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>(1) Meshes generated by the modeling tools are created with zero collision primitives, and setting a Collision Preset only defines the collision response, not the collision geometry. Resolved by adding simplified collision to the source static mesh assets. (2) Simplified box collision encloses the entire mesh and seals boolean-carved apertures. Resolved by removing the simplified collision and setting Collision Complexity to Use Complex Collision As Simple on the affected wall assets, so the render geometry is used for collision and the openings remain passable. Both fixes were made on the source assets, so every copy-pasted instance inherited them. Retested and passed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -931,12 +931,12 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Minimum of one timed puzzle required per design doc.</t>
+          <t>Minimum of one timed puzzle required per design doc; requirement is retained, not removed. Rescheduled to the Final phase for Milestone Two so the Alpha build concentrates on the environmental puzzle, health/defeat loop, HUD, and level blockout.</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>No asset packs or Starter Content per design doc. Outdoor surface approach and enterable entrance building blocked out 2026-07-27 using the engine modeling tools; interior vault rooms outstanding.</t>
+          <t>No asset packs or Starter Content per design doc. Level blocked out 2026-07-27 using the engine modeling tools within the existing map: outdoor surface approach, an enterable entrance building with a door and windows, and the puzzle area. All geometry is primitive-based with no imported assets.</t>
         </is>
       </c>
     </row>
@@ -2231,10 +2231,18 @@
           <t>Trigger the timed puzzle. Confirm countdown timer appears and counts down correctly. Let timer expire — confirm failure/reset occurs. Complete puzzle before timer — confirm success fires.</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="56.1" customHeight="1" s="10">
       <c r="A11" s="14" t="inlineStr">
@@ -2412,7 +2420,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Walk the level end-to-end without reading any documentation. Confirm the layout naturally guides the player toward each puzzle and then the boss without explicit waypoints.</t>
+          <t>Walk the level end to end without reading any documentation. Confirm the layout naturally guides the player from the outdoor approach, through the entrance building, and into the puzzle area using sightlines and framing rather than explicit waypoints. Boss arena routing is deferred to the Final phase.</t>
         </is>
       </c>
       <c r="C20" s="13" t="n"/>

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -899,12 +899,12 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Partially implemented: CurrentHealth variable and turret damage are working and defeat triggers, but the defeat path currently quits the game. Restart via OpenLevel is outstanding - tracked with the Lose Condition row.</t>
+          <t>Implemented on BP_PlayerChar via Event AnyDamage. Defeat threshold corrected to Health &lt;= 0.0 during testing. Merged via feature/death-restart.</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Rescoped to Alpha for Milestone Two: a simple lose state plus OpenLevel restart is required so the health/defeat loop is testable. The styled Lose screen widget remains in Final.</t>
+          <t>Rescoped to Alpha for Milestone Two: defeat now prints a lose message and reloads the level via Open Level, replacing the previous Quit Game behaviour. The styled Lose screen widget remains in Final. Merged via feature/death-restart.</t>
         </is>
       </c>
     </row>
@@ -2212,13 +2212,29 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Use a debug key or damage volume to reduce player health. Confirm health bar decrements. Reduce to 0 and confirm Lose screen displays and game pauses.</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
+          <t>Take turret fire in PIE. Confirm Health decrements by the damage amount on each hit using the debug print. Continue taking damage until Health reaches zero and confirm the defeat branch fires.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Defeat did not fire when Health reached exactly zero. The player remained alive at zero health until a further hit pushed the value negative, so defeat always triggered one hit late.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Root cause was a strict less-than comparison (Health &lt; 0.0) on the defeat branch, which evaluates false at exactly zero. Changed to less-than-or-equal (Health &lt;= 0.0) so defeat fires as soon as health is depleted. Retested against turret damage and defeat now triggers on the hit that brings health to zero.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="56.1" customHeight="1" s="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2356,13 +2372,29 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Reduce player health to 0. Confirm Lose screen displays. Press Restart — confirm level reloads cleanly with all state reset (health, timer, puzzles).</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
+          <t>Reduce player health to zero using turret fire. Confirm the defeat message is displayed, then confirm the level reloads automatically and that health, collectibles, and door state are reset on the new run.</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Defeat closed the application instead of restarting the level, ending the play session entirely.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Root cause was a Quit Game node wired to the defeat branch. Replaced with a lose message, a 1.5 second delay, and an Open Level call targeting TestEnvironment. Reloading the map rebuilds the player character from its default values, so health, collectibles, and door state reset without any additional wiring. Retested and the level reloads cleanly. The styled Lose screen widget with a Restart button remains scheduled for the Final phase.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="56.1" customHeight="1" s="10">
       <c r="A17" s="14" t="inlineStr">

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -2135,10 +2135,26 @@
           <t>Enter PIE. Verify camera is at eye level. Move mouse to confirm look rotates correctly in X and Y. Check no roll occurs.</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="56.1" customHeight="1" s="10">
       <c r="A5" s="14" t="inlineStr">
@@ -2151,10 +2167,26 @@
           <t>In PIE, press W/A/S/D and verify character moves in correct directions relative to camera facing. Check no input bleeds across axes.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="56.1" customHeight="1" s="10">
       <c r="A6" s="12" t="inlineStr">
@@ -2167,10 +2199,26 @@
           <t>Move mouse in all directions; confirm pitch clamps at ~80° up/down. Verify yaw is unclamped. Check look speed feels natural.</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="56.1" customHeight="1" s="10">
       <c r="A7" s="14" t="inlineStr">
@@ -2183,10 +2231,26 @@
           <t>Press Spacebar in PIE. Confirm character leaves the ground and lands correctly. Verify jump cannot be triggered mid-air (no double-jump unless intended).</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="56.1" customHeight="1" s="10">
       <c r="A8" s="12" t="inlineStr">
@@ -2199,10 +2263,26 @@
           <t>Place a test actor implementing interface_interact. Walk within range and press E and LMB separately. Confirm print string fires for both inputs. Confirm out-of-range does not fire.</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="56.1" customHeight="1" s="10">
       <c r="A9" s="14" t="inlineStr">
@@ -2271,10 +2351,26 @@
           <t>Carry each colored object onto its matching colored button. Confirm a button only presses for an object of its own colour and ignores mismatched objects. Confirm the door opens once every button is satisfied. Remove an object and confirm that button releases and the door re-locks.</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>No gameplay defects. During development the containing asset folder was misnamed, which left stale redirectors pointing at the button, door and material assets.</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Folder renamed to AnimatedInteractables and the stale redirectors deleted so the assets resolve to a single canonical path. Committed as 0dfcc93. Puzzle behaviour was unaffected and retested afterwards: buttons respond only to a matching colour and the door opens once all are satisfied.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="56.1" customHeight="1" s="10">
       <c r="A12" s="12" t="inlineStr">
@@ -2287,10 +2383,26 @@
           <t>Test all actors implementing interface_interact. Confirm line trace from camera hits each one within expected range. Confirm interface call does not error on any actor.</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="56.1" customHeight="1" s="10">
       <c r="A13" s="14" t="inlineStr">
@@ -2455,10 +2567,26 @@
           <t>Walk the level end to end without reading any documentation. Confirm the layout naturally guides the player from the outdoor approach, through the entrance building, and into the puzzle area using sightlines and framing rather than explicit waypoints. Boss arena routing is deferred to the Final phase.</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Walked end to end with no documentation. The entrance building is visible from the starting area and each doorway frames the next space, so the route reads without waypoints or markers.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="56.1" customHeight="1" s="10">
       <c r="A21" s="14" t="inlineStr">
@@ -2471,10 +2599,26 @@
           <t>Review Content Browser. Confirm no Starter Content folder, no Marketplace assets. All meshes and materials are custom or created within the project.</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Content Browser audited: no Starter Content folder and no marketplace or Fab assets present. All 17 project assets are authored in-project, and level geometry is primitive-based, built with the engine modeling tools.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="56.1" customHeight="1" s="10">
       <c r="A22" s="12" t="inlineStr">
@@ -2519,10 +2663,26 @@
           <t>Review GitHub repo. Confirm a branch exists per major feature. Confirm each branch was merged via pull request. Confirm PRs reference resolved issues.</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Repository audited. Every feature was developed on its own branch (playerSetup, feature/pickup-interaction, feature/door-setup, feature/turret, feature/button-setup, feature/level-blockout, feature/death-restart) and merged into main through a pull request.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="56.1" customHeight="1" s="10">
       <c r="A25" s="14" t="inlineStr">
@@ -2535,10 +2695,26 @@
           <t>Review commit history. Confirm commits are frequent (not just milestone-end dumps). Confirm commit messages describe the feature added (e.g., 'feat: implement pressure plate overlap logic').</t>
         </is>
       </c>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Early commits tracked Unreal's generated folders and stored binary assets outside Git LFS, inflating the repository.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Resolved in 2b3a163 and 9b959df: .gitignore corrected for the nested project layout, generated folders untracked, and .uasset/.umap moved to Git LFS. Commits since use feat/chore/docs prefixes naming the feature addressed, and are made per logical unit of work rather than at milestone ends.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="56.1" customHeight="1" s="10">
       <c r="A26" s="12" t="inlineStr">
@@ -2551,10 +2727,26 @@
           <t>Grab a movable physics object via the interact line trace. Confirm it attaches in front of the camera and follows player movement. Drop it and confirm physics resume. Place it on a pressure plate and confirm the plate registers it.</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="12" t="inlineStr"/>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="56.1" customHeight="1" s="10">
       <c r="A27" s="14" t="inlineStr">
@@ -2567,10 +2759,26 @@
           <t>Overlap a collectible and press interact. Confirm it is collected only on input (not on overlap alone), destroys itself, and increments the HUD counter. Verify a gated door/terminal checks the count correctly before allowing progression.</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr"/>
-      <c r="F27" s="14" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="56.1" customHeight="1" s="10">
       <c r="A28" s="12" t="inlineStr">
@@ -2631,10 +2839,26 @@
           <t>Enter the turret's detection range. Confirm it rotates to track the player and begins firing on a fixed interval. Confirm projectiles travel, collide, and are destroyed on impact. Take a hit and confirm player health decrements. Leave range and confirm the turret stops firing.</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="56.1" customHeight="1" s="10">
       <c r="A31" s="14" t="inlineStr">

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -1991,12 +1991,12 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Design doc requires all code be commented.</t>
+          <t>Design doc requires all code be commented. Comment boxes added across the project blueprints and re-audited during Milestone Two testing.</t>
         </is>
       </c>
     </row>
@@ -2631,10 +2631,26 @@
           <t>Open every Blueprint created. Confirm each node group has a Comment Box. Confirm no large uncommented graph sections exist.</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Initial pass found node groups in the player, interactable and turret blueprints with no comment boxes, which did not meet the design document requirement that all code be commented.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Comment boxes added over each logical node group across the project blueprints, including the movement, look, jump, interact and damage/defeat sections of BP_PlayerChar. Re-audited afterwards with no uncommented groups remaining.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="56.1" customHeight="1" s="10">
       <c r="A23" s="14" t="inlineStr">
@@ -2856,7 +2872,7 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>No changes required. Behaviour matched the expected result on the first pass.</t>
+          <t>No changes required. The turret tracks the player, fires on an interval, and its projectile applies damage that decrements player health, which is the damage source used to exercise the defeat loop.</t>
         </is>
       </c>
     </row>

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -2038,12 +2038,12 @@
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Explicit requirement in design doc Code section.</t>
+          <t>Explicit requirement in design doc Code section. Project-wide Find in Blueprints audit completed during Milestone Two testing: the only Event Tick nodes present are disabled default stubs.</t>
         </is>
       </c>
     </row>
@@ -2660,13 +2660,29 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Open all Blueprints. Search for Event Tick nodes. Confirm each Tick usage is cosmetic only. Confirm all looping game logic uses Timer by Event or Timer by Function Name.</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
+          <t>Audit all blueprints for Event Tick using Find in Blueprints (Ctrl+Shift+F) across the whole project. Confirm any Tick usage is cosmetic only, and that all looping game logic runs on Timer by Event or Timer by Function Name.</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Project-wide search returned Event Tick in four project blueprints (BP_GameMode, BP_CollectiblePIckup, BP_Button and WBP_HUD). All four are the default stub node Unreal adds to a new blueprint, each flagged "This node is disabled and will not be called" with no execution wired to it, so none of them run. All remaining results were engine and plugin content outside the project. No changes required. Looping logic in the project uses Timer by Event.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="56.1" customHeight="1" s="10">
       <c r="A24" s="12" t="inlineStr">

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -1408,10 +1408,14 @@
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Implemented in WBP_HUD and displayed on Event Construct, collapsing after eight seconds so the brief does not persist through play.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="51.95" customHeight="1" s="10">
       <c r="A23" s="12" t="inlineStr">
@@ -1451,12 +1455,12 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Required per design doc.</t>
+          <t>Required per design doc. Progress Bar in WBP_HUD bound to player Health via a Percent binding function.</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2520,29 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Load the level. Confirm the objective widget appears at the start point. Verify text is readable and widget dismisses correctly (by input or timeout).</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
+          <t>Load the level. Confirm the objective text appears on screen at the start point, is readable against the level geometry, and dismisses itself after the set time.</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>No changes required. The objective is displayed by WBP_HUD on Event Construct and collapses after eight seconds via a Delay into Set Visibility, so it briefs the player without needing an input to dismiss it.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="56.1" customHeight="1" s="10">
       <c r="A18" s="12" t="inlineStr">
@@ -2532,13 +2552,29 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Confirm health bar is visible on HUD from game start. Take damage — confirm bar decrements in real time. Heal (if applicable) — confirm bar increments.</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
+          <t>Confirm the health bar is visible on the HUD from game start. Take turret fire and confirm the bar decrements in real time as Health decreases.</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>The bar initially stayed empty and did not respond to damage. The binding function returned a hardcoded 0.0.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Root cause was two unconnected pins in the Percent binding: the Cast to BP_PlayerChar node sat outside the execution path, and the divide result was never wired to the Return node, so the function always returned its default 0.0. Resolved by routing execution through the Cast and connecting Health divided by 100 into Return Value. Retested and the bar now fills at full health and decrements on each turret hit.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="56.1" customHeight="1" s="10">
       <c r="A19" s="14" t="inlineStr">

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -1487,12 +1487,12 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Required per design doc.</t>
+          <t>Required per design doc; requirement retained, not removed. The one second counter is implemented in WBP_HUD using Set Timer by Event, satisfying the design doc rule that looping logic avoid Event Tick. The MM:SS text binding that displays it is rescheduled to the Final phase for Milestone Two.</t>
         </is>
       </c>
     </row>
@@ -2587,10 +2587,18 @@
           <t>Confirm timer starts at 0:00 on level load and increments each second. Confirm timer stops on Win or Lose condition. Verify MM:SS format is correct past 9:59.</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="D19" s="14" t="n"/>
       <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Deferred to Final phase per the rescoped traceability matrix. The underlying one second counter is built and running on Timer by Event; the MM:SS text binding that surfaces it is not implemented in the Alpha build, so the timer field displays its placeholder value.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="56.1" customHeight="1" s="10">
       <c r="A20" s="12" t="inlineStr">

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -1487,12 +1487,12 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Required per design doc; requirement retained, not removed. The one second counter is implemented in WBP_HUD using Set Timer by Event, satisfying the design doc rule that looping logic avoid Event Tick. The MM:SS text binding that displays it is rescheduled to the Final phase for Milestone Two.</t>
+          <t>Required per design doc. ElapsedSeconds is driven by Set Timer by Event on a one second loop and displayed through a TimerText binding that formats it as MM:SS, so no looping logic runs on Event Tick.</t>
         </is>
       </c>
     </row>
@@ -2584,19 +2584,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Confirm timer starts at 0:00 on level load and increments each second. Confirm timer stops on Win or Lose condition. Verify MM:SS format is correct past 9:59.</t>
+          <t>Confirm the timer starts at 00:00 on level load and increments once per second. Verify the MM:SS format is correct, including padding below ten and the rollover from 00:59 to 01:00.</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Not Tested</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>The timer initially displayed 1:00, 2:00, 3:00. Minutes and seconds were reversed, and one of the two integer-to-text conversions was not zero padded.</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix. The underlying one second counter is built and running on Timer by Event; the MM:SS text binding that surfaces it is not implemented in the Alpha build, so the timer field displays its placeholder value.</t>
+          <t>Root cause was the two Format Text arguments being wired to the wrong pins, so the modulo result (seconds) fed the minutes slot and the divide result (minutes) fed the seconds slot. Swapped the connections and set Minimum Integral Digits to 2 on both To Text (Integer) nodes. Retested: the field now reads 00:01 upward and rolls over to 01:00 correctly. The counter itself runs on Set Timer by Event rather than Event Tick, per the design document.</t>
         </is>
       </c>
     </row>

--- a/docs/GAM303_Traceability_and_Test_Plan.xlsx
+++ b/docs/GAM303_Traceability_and_Test_Plan.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Minimum of one timed puzzle required per design doc; requirement is retained, not removed. Rescheduled to the Final phase for Milestone Two so the Alpha build concentrates on the environmental puzzle, health/defeat loop, HUD, and level blockout.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="51.95" customHeight="1" s="10">
       <c r="A19" s="12" t="inlineStr">
@@ -1276,7 +1280,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Boss fight must utilize skills learned earlier in the level.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1325,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="51.95" customHeight="1" s="10">
       <c r="A21" s="12" t="inlineStr">
@@ -1554,7 +1562,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Listed in design doc UI section. Rescoped to Final for Milestone Two; not required for the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1609,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Listed in design doc UI section.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1654,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr"/>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="51.95" customHeight="1" s="10">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Level Design</t>
+          <t>UI / HUD</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Level Blockout</t>
+          <t>Main Menu</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Block out the entire level using BSP or cube meshes. No asset packs or Starter Content. Layout must naturally guide the player without mechanical handholding.</t>
+          <t>Widget Blueprint (MainMenu_W) on a dedicated MainMenuMap, with Play and Quit buttons and an intro animation. Play calls Open Level to load TestEnvironment; Quit calls Quit Game.</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -1671,12 +1683,12 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Pre-Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -1691,7 +1703,7 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>No asset packs or Starter Content per design doc. Level blocked out 2026-07-27 using the engine modeling tools within the existing map: outdoor surface approach, an enterable entrance building with a door and windows, and the puzzle area. All geometry is primitive-based with no imported assets.</t>
+          <t>Built from the Module Six menu widget and animation tutorials. Not yet set as the project GameDefaultMap, so TestEnvironment still loads on play and the menu is entered from MainMenuMap.</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1715,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Puzzle Area 1 — Timed</t>
+          <t>Level Blockout</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Design and dress the timed puzzle room within the blocked-out level. Integrate timed puzzle Blueprint. Ensure room teaches the interact mechanic before requiring it under pressure.</t>
+          <t>Block out the entire level using BSP or cube meshes. No asset packs or Starter Content. Layout must naturally guide the player without mechanical handholding.</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -1718,12 +1730,12 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Pre-Alpha</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -1733,10 +1745,14 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>No asset packs or Starter Content per design doc. Level blocked out 2026-07-27 using the engine modeling tools within the existing map: outdoor surface approach, an enterable entrance building with a door and windows, and the puzzle area. All geometry is primitive-based with no imported assets.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="51.95" customHeight="1" s="10">
       <c r="A30" s="12" t="inlineStr">
@@ -1746,12 +1762,12 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Puzzle Area 2 — Environmental</t>
+          <t>Puzzle Area 1 — Timed</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Design and dress the environmental puzzle room. Integrate pressure plate and physics object setup. Room must be completable without external instruction.</t>
+          <t>Design and dress the timed puzzle room within the blocked-out level. Integrate timed puzzle Blueprint. Ensure room teaches the interact mechanic before requiring it under pressure.</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -1779,7 +1795,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr"/>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="51.95" customHeight="1" s="10">
       <c r="A31" s="12" t="inlineStr">
@@ -1789,12 +1809,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Boss Arena</t>
+          <t>Puzzle Area 2 — Environmental</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Design the boss arena with all environmental defeat mechanics placed and clearly readable. Arena layout must reinforce skills practiced in the two puzzle areas.</t>
+          <t>Design and dress the environmental puzzle room. Integrate pressure plate and physics object setup. Room must be completable without external instruction.</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1819,89 +1839,93 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Built as part of the level blockout. The colored-button puzzle and its door are integrated into the room, and the door is visible from the entrance so the objective reads without instruction.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="51.95" customHeight="1" s="10">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>Level Design</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Boss Arena</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Design the boss arena with all environmental defeat mechanics placed and clearly readable. Arena layout must reinforce skills practiced in the two puzzle areas.</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Unreal Engine 5</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51.95" customHeight="1" s="10">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Feature Branching</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Create a branch per feature (e.g., feature/player-movement, feature/timed-puzzle). Merge via pull request when feature is complete and tested. Tag PR with resolved issue.</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>GitHub / Git</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Pre-Alpha</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Required per design doc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" s="10">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Commit Discipline</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Label every commit with the feature it addresses (e.g., 'feat: add jump input action'). Commit after each logical unit of work — not just at milestones.</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>GitHub / Git</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>Pre-Alpha</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
           <t>Self</t>
@@ -1909,10 +1933,14 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Required per design doc. Seven feature branches merged to main through pull requests #1-#12: playerSetup, pickup-interaction, door-setup, turret, button-setup, level-blockout, death-restart, hud, and main-menu.</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="10">
       <c r="A34" s="12" t="inlineStr">
@@ -1922,17 +1950,17 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Issue / Task Tracking</t>
+          <t>Commit Discipline</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Create a GitHub Issue for each row in this traceability matrix. Resolve issue and reference it in the pull request when the feature branch is merged.</t>
+          <t>Label every commit with the feature it addresses (e.g., 'feat: add jump input action'). Commit after each logical unit of work — not just at milestones.</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>GitHub / Git</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1952,30 +1980,34 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>Commits use feat/chore/docs prefixes naming the feature addressed and are made per logical unit of work rather than at milestone ends. 38 commits across the project.</t>
+        </is>
+      </c>
     </row>
     <row r="35" s="10">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Code Quality</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Blueprint Comments</t>
+          <t>Issue / Task Tracking</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Every Blueprint node group must have a Comment Box describing its purpose. Complex event graphs should have section headers. Required by design doc.</t>
+          <t>Create a GitHub Issue for each row in this traceability matrix. Resolve issue and reference it in the pull request when the feature branch is merged.</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Unreal Engine 5</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1995,12 +2027,12 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Design doc requires all code be commented. Comment boxes added across the project blueprints and re-audited during Milestone Two testing.</t>
+          <t>Not implemented as GitHub Issues. Task tracking was carried out through feature branches, pull requests and this traceability matrix instead, which covered the same need without duplicating the row list in a second system. Recorded here rather than removed so the decision is visible.</t>
         </is>
       </c>
     </row>
@@ -2012,40 +2044,87 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
+          <t>Blueprint Comments</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Every Blueprint node group must have a Comment Box describing its purpose. Complex event graphs should have section headers. Required by design doc.</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Unreal Engine 5</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Pre-Alpha</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Design doc requires all code be commented. Comment boxes added across the project blueprints and re-audited during Milestone Two testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="10">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Code Quality</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
           <t>No Tick Misuse</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Audit all Blueprints before submission. Event Tick may only drive visual/cosmetic updates. All looping logic must use Timer by Event or Timer by Function Name.</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Unreal Engine 5</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>Explicit requirement in design doc Code section. Project-wide Find in Blueprints audit completed during Milestone Two testing: the only Event Tick nodes present are disabled default stubs.</t>
         </is>
@@ -2066,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="10" min="1" max="1"/>
@@ -2340,7 +2419,7 @@
       <c r="E10" s="12" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2507,7 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2531,7 @@
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2555,7 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2963,7 @@
       <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2987,7 @@
       <c r="E29" s="14" t="inlineStr"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Deferred to Final phase per the rescoped traceability matrix; feature is not implemented in the Alpha build.</t>
+          <t>Not implemented in the final prototype. Scope was reduced during Milestone Two to protect the delivery date, prioritising the core gameplay loop, level blockout and HUD over the boss encounter. The requirement is retained in this matrix rather than removed so the traceability record stays complete.</t>
         </is>
       </c>
     </row>
@@ -2973,6 +3052,38 @@
       <c r="F31" s="14" t="inlineStr">
         <is>
           <t>(1) Meshes generated by the modeling tools are created with zero collision primitives, and setting a Collision Preset only defines the collision response, not the collision geometry. Resolved by adding simplified collision to the source static mesh assets. (2) Simplified box collision encloses the entire mesh and seals boolean-carved apertures. Resolved by removing the simplified collision and setting Collision Complexity to Use Complex Collision As Simple on the affected wall assets, so the render geometry is used for collision and the openings remain passable. Both fixes were made on the source assets, so every copy-pasted instance inherited them. Retested and passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56.1" customHeight="1" s="10">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Main Menu</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Open MainMenuMap and play. Confirm the menu widget appears with its intro animation and that the cursor is usable. Click Play and confirm TestEnvironment loads. Return and click Quit, confirming the game exits.</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>None. No runtime errors or blueprint warnings were logged in the Output Log.</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>No changes required. Both buttons behave as expected and the animation plays on open. The menu is reached from MainMenuMap rather than being the project default map, which is recorded on the matrix row.</t>
         </is>
       </c>
     </row>
